--- a/data/trans_camb/P1432-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1432-Edad-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,0</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-0,97; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,48; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,0</t>
+          <t>-0,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,0</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,0</t>
+          <t>-0,69; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,0</t>
+          <t>-0,6; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,0</t>
+          <t>-0,58; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,59</t>
+          <t>-0,66; 0,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,42</t>
+          <t>-0,59; 0,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,88</t>
+          <t>-0,44; 0,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,4</t>
+          <t>-0,47; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,27</t>
+          <t>-0,54; 0,23</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,25; 516,34</t>
+          <t>-100,0; 372,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,66</t>
+          <t>-0,74; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,15</t>
+          <t>-0,92; 0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,6</t>
+          <t>-1,26; 0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,67</t>
+          <t>-1,16; 0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,38</t>
+          <t>-0,86; 0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,32</t>
+          <t>-0,86; 0,31</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,36; 396,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 175,53</t>
+          <t>-87,24; 154,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 150,42</t>
+          <t>-87,27; 145,43</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,48</t>
+          <t>-1,87; 0,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,03</t>
+          <t>-2,34; -0,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,98</t>
+          <t>-1,96; 1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,41</t>
+          <t>-2,45; 1,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,97</t>
+          <t>-1,56; 0,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,39</t>
+          <t>-2,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 368,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,52; 175,7</t>
+          <t>-59,76; 162,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 132,88</t>
+          <t>-72,39; 142,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,85; 102,47</t>
+          <t>-64,73; 90,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 42,43</t>
+          <t>-77,75; 48,29</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,93</t>
+          <t>-2,93; 3,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,77</t>
+          <t>-5,8; -0,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,37</t>
+          <t>-3,35; 2,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,53</t>
+          <t>-3,53; 1,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,94</t>
+          <t>-2,35; 2,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,01</t>
+          <t>-3,69; -0,23</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 193,13</t>
+          <t>-61,32; 174,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-95,52; -9,45</t>
+          <t>-95,39; -3,18</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 123,75</t>
+          <t>-72,37; 111,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 102,43</t>
+          <t>-73,18; 85,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 79,75</t>
+          <t>-51,73; 87,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 8,75</t>
+          <t>-79,2; -5,44</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -1,87</t>
+          <t>-9,71; -1,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,49</t>
+          <t>-7,13; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,06</t>
+          <t>-2,44; 6,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,98</t>
+          <t>-3,8; 4,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,87</t>
+          <t>-3,87; 2,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,8</t>
+          <t>-4,15; 1,69</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-91,83; -28,18</t>
+          <t>-92,57; -24,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 39,67</t>
+          <t>-70,93; 28,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 132,31</t>
+          <t>-31,44; 141,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 93,92</t>
+          <t>-45,15; 90,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 38,45</t>
+          <t>-45,8; 44,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 33,16</t>
+          <t>-48,96; 30,06</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,02</t>
+          <t>-0,88; 0,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; -0,14</t>
+          <t>-1,03; -0,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,78</t>
+          <t>-0,48; 0,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,58</t>
+          <t>-0,67; 0,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,2</t>
+          <t>-0,56; 0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,07</t>
+          <t>-0,63; 0,07</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 2,06</t>
+          <t>-65,09; 11,48</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-74,3; -17,1</t>
+          <t>-75,09; -19,43</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 66,75</t>
+          <t>-27,75; 62,11</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 50,63</t>
+          <t>-37,37; 44,79</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 18,4</t>
+          <t>-37,29; 18,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 8,09</t>
+          <t>-43,77; 6,21</t>
         </is>
       </c>
     </row>
